--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/abr-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2106,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2236,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2301,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2427,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2492,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2740,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2805,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2870,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2935,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3061,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3187,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3252,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3317,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3382,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3447,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3512,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3577,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3642,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3707,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3833,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3898,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3963,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4028,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4093,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4158,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4223,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4288,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4353,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4418,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4483,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4609,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4674,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4739,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4804,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4869,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4934,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +4999,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5064,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5129,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5316,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5381,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5446,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5511,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5576,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5641,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5767,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5832,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5897,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5962,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6027,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6092,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6157,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6222,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6287,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6352,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6478,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6543,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6608,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6673,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6609,7 +6925,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +6990,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +7055,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7120,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6853,7 +7185,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6975,7 +7311,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7376,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7441,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7506,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7280,7 +7632,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7341,7 +7697,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7463,7 +7823,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7585,7 +7949,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8136,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8201,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8266,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8331,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8396,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8461,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8526,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8591,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8656,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8721,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8786,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +8912,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +8977,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +9042,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9107,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9172,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9237,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9302,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9428,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9049,7 +9493,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9558,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9684,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9810,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9875,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +9940,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +10066,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10192,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10379,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10444,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10025,7 +10509,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10574,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10147,7 +10639,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10334,7 +10830,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10456,7 +10956,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10578,7 +11082,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10639,7 +11147,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10761,7 +11273,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10822,7 +11338,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10883,7 +11403,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10944,7 +11468,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11005,7 +11533,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11127,7 +11659,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11188,7 +11724,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11249,7 +11789,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11310,7 +11854,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11432,7 +11980,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11493,7 +12045,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11615,7 +12171,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11737,7 +12297,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
